--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -743,32 +743,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -776,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +804,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -854,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -887,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +923,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -965,32 +981,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -998,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1042,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1172,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1159,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1201,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1220,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1234,7 +1258,7 @@
       <c r="T7" s="2" t="inlineStr"/>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1270,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1405,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1413,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>07:25</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1461,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1456,7 +1480,7 @@
       <c r="T9" s="2" t="inlineStr"/>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1492,7 +1516,681 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -872,24 +872,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -991,24 +991,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -1100,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1157,17 +1161,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1177,13 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1283,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1322,32 +1330,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1355,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1379,33 +1391,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -1433,32 +1449,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1466,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1490,33 +1510,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1616,7 +1640,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1688,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1727,7 +1751,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1799,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1838,7 +1862,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1853,7 +1877,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1938,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,7 +2049,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2074,12 +2098,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -2087,22 +2111,22 @@
       <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>沪A67983D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2140,7 +2164,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2154,43 +2178,840 @@
       <c r="T15" s="2" t="inlineStr"/>
       <c r="U15" s="2" t="inlineStr">
         <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X15" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y15" s="2" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z15" s="2" t="inlineStr">
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr"/>
-      <c r="AC15" s="2" t="inlineStr">
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>4/10</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,13 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -780,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1137,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,14 +1180,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>73.0</t>
@@ -1191,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1367,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1486,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1540,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1679,32 +1683,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1712,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1736,17 +1744,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1756,13 +1764,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1877,7 +1889,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1905,32 +1917,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -1938,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1962,33 +1978,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2088,7 +2108,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2131,32 +2151,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2164,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2188,37 +2212,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -2246,32 +2270,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2279,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2303,29 +2331,29 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>73.0</t>
@@ -2333,7 +2361,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2509,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2548,7 +2576,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2620,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2674,7 +2702,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,7 +2874,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2890,13 +2918,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -2904,22 +2936,22 @@
       <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2952,12 +2984,12 @@
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2971,47 +3003,618 @@
       <c r="T22" s="2" t="inlineStr"/>
       <c r="U22" s="2" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>09:18</t>
         </is>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y22" s="2" t="inlineStr">
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z22" s="2" t="inlineStr">
+      <c r="Z23" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
+      <c r="AA23" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
+      <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="AC22" s="2" t="inlineStr">
-        <is>
-          <t>4/10</t>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>6/10</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,13 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1415,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1544,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1720,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1835,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1954,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2008,7 +2012,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2123,7 +2127,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2242,7 +2246,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -2280,24 +2284,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2307,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2356,12 +2360,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -2389,32 +2393,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2422,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2446,17 +2454,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2466,17 +2474,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -2504,32 +2512,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2537,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2561,17 +2573,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2581,13 +2593,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2687,7 +2703,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2702,7 +2718,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2802,7 +2818,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2874,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2989,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3043,7 +3059,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3219,7 +3235,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3273,7 +3289,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3388,7 +3404,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3465,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3493,13 +3509,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3580,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3609,12 +3629,238 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>8/10</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>10/10</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,13 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1768,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1878,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,22 +2116,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2311,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2350,7 +2354,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2365,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -2403,12 +2407,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -2430,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,22 +2473,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -2522,24 +2526,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2549,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2598,12 +2602,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -2631,32 +2635,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -2664,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2688,17 +2696,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2708,17 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>10/10</t>
         </is>
       </c>
     </row>
@@ -2746,32 +2754,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2779,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2803,17 +2815,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2823,13 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2873,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2890,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2914,17 +2934,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2934,17 +2954,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -2972,32 +2992,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3005,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3029,37 +3053,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -3087,32 +3111,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3120,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3144,37 +3172,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3317,32 +3345,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3350,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3374,37 +3406,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3514,12 +3546,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3619,7 +3651,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3634,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3739,13 +3771,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3850,17 +3886,592 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>10/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>69.5</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>7/10</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -3230,32 +3230,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3263,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3287,37 +3291,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -3355,24 +3359,24 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3382,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3431,12 +3435,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -3464,32 +3468,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3497,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3521,17 +3529,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3541,17 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -3579,32 +3587,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3612,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3636,17 +3648,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3656,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -3694,32 +3706,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3727,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3751,17 +3767,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3771,12 +3787,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3809,32 +3825,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -3842,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3866,27 +3886,27 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3924,32 +3944,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3957,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3981,17 +4005,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4001,17 +4025,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4111,7 +4135,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4126,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4236,12 +4260,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4356,7 +4380,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4461,17 +4485,477 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>69.7</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="AC34" s="2" t="inlineStr">
-        <is>
-          <t>7/10</t>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>6/10</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>10/10</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,17 +1414,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2121,17 +2121,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>10/10</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,17 +2473,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3430,17 +3430,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>10/10</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3835,24 +3835,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3911,12 +3911,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -4063,32 +4063,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -4096,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4120,17 +4124,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4140,17 +4144,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -4178,32 +4182,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4211,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4235,17 +4243,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4255,17 +4263,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>10/10</t>
         </is>
       </c>
     </row>
@@ -4293,32 +4301,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4326,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4350,32 +4362,32 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4408,32 +4420,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4441,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4465,17 +4481,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4485,17 +4501,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4595,7 +4611,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4671,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4720,12 +4736,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4901,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4945,15 +4961,475 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>71.7</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="AC38" s="2" t="inlineStr">
+      <c r="AC42" s="2" t="inlineStr">
         <is>
           <t>6/10</t>
         </is>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,22 +3663,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4144,17 +4144,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -4430,24 +4430,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -4539,32 +4539,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4572,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4596,17 +4600,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4616,17 +4620,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -4654,32 +4658,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4687,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4711,17 +4719,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4731,12 +4739,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4769,32 +4777,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4802,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4826,37 +4838,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -4884,32 +4896,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -4917,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4941,17 +4957,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4961,17 +4977,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5071,7 +5087,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5147,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5186,7 +5202,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5201,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5306,17 +5322,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5350,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5377,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5391,7 +5407,7 @@
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5431,7 +5447,467 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>69.8</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>3/10</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2478,17 +2478,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4620,17 +4620,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4787,24 +4787,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -4906,12 +4906,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -5015,32 +5015,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5048,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5072,17 +5076,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5092,17 +5096,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -5130,32 +5134,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5163,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5187,17 +5195,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5207,17 +5215,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -5245,32 +5253,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5278,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5302,17 +5314,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5322,17 +5334,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5432,7 +5444,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5508,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5557,12 +5569,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5662,7 +5674,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5738,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5782,17 +5794,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5897,17 +5909,362 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>69.5</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB46" s="2" t="inlineStr">
-        <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="AC46" s="2" t="inlineStr">
-        <is>
-          <t>3/10</t>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>5/10</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,17 +942,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,17 +2235,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,22 +2473,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,17 +3306,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,22 +4377,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4501,17 +4501,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,17 +4853,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,17 +5096,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,22 +5210,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5487,32 +5487,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5520,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5544,32 +5548,32 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5602,32 +5606,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5635,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5659,17 +5667,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5679,17 +5687,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -5717,32 +5725,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5750,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5774,17 +5786,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5794,17 +5806,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -5832,32 +5844,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5865,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5889,37 +5905,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6095,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6134,7 +6150,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6157,22 +6173,22 @@
       <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>沪A67983D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6210,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6224,47 +6240,622 @@
       <c r="T49" s="2" t="inlineStr"/>
       <c r="U49" s="2" t="inlineStr">
         <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
           <t>15:51</t>
         </is>
       </c>
-      <c r="V49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W49" s="2" t="inlineStr">
+      <c r="W50" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X49" s="2" t="inlineStr">
+      <c r="X50" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y49" s="2" t="inlineStr">
+      <c r="Y50" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z49" s="2" t="inlineStr">
+      <c r="Z50" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>72.8</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB49" s="2" t="inlineStr">
+      <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="AC49" s="2" t="inlineStr">
+      <c r="AC51" s="2" t="inlineStr">
         <is>
           <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>9/10</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,17 +704,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,17 +1767,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,17 +2949,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,22 +3187,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,22 +4020,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4501,17 +4501,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,17 +4615,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,17 +5329,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,22 +5444,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5687,17 +5687,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5963,32 +5963,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5996,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6020,37 +6024,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -6078,32 +6082,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6111,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6135,17 +6143,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6155,12 +6163,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6193,32 +6201,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6226,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6250,32 +6262,32 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6308,32 +6320,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6341,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6365,17 +6381,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6385,17 +6401,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6495,7 +6511,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6571,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6620,7 +6636,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6686,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6801,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6845,17 +6861,592 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>9/10</t>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>70.8</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>72.8</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>6/10</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2478,17 +2478,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4144,17 +4144,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4501,17 +4501,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4977,17 +4977,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5215,17 +5215,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5687,17 +5687,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6211,24 +6211,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -6320,36 +6320,32 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6357,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6381,17 +6377,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6401,17 +6397,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -6439,32 +6435,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6496,17 +6496,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6516,17 +6516,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -6554,32 +6554,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6587,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6611,17 +6615,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6631,17 +6635,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6741,7 +6745,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6817,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6932,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6986,7 +6990,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7096,12 +7100,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7166,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7277,7 +7281,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7321,17 +7325,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7446,7 +7450,122 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>1/10</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2478,17 +2478,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,17 +3663,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5215,17 +5215,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6320,32 +6320,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6353,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6377,32 +6381,32 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6445,24 +6449,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6472,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6521,12 +6525,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -6554,36 +6558,32 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6615,17 +6615,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6635,17 +6635,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7569,6 +7569,466 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,17 +1533,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>72.0</t>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,14 +3068,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>72.0</t>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,17 +3901,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,14 +4139,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>72.0</t>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4620,17 +4620,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,17 +4734,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,14 +4972,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>72.0</t>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,17 +5096,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,17 +5334,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5806,17 +5806,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,17 +6158,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6282,17 +6282,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6515,14 +6515,14 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>72.0</t>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6788,32 +6788,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6821,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6845,32 +6849,32 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6903,32 +6907,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6936,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6960,17 +6968,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6980,17 +6988,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -7018,32 +7026,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7051,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7075,17 +7087,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7095,17 +7107,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -7133,32 +7145,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7166,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7190,17 +7206,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7210,17 +7226,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -7248,32 +7264,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7281,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7305,29 +7325,29 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
           <t>72.0</t>
@@ -7335,7 +7355,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7435,7 +7455,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7450,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7626,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7665,7 +7685,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7741,7 +7761,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7785,17 +7805,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7876,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7971,7 +7991,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8015,17 +8035,477 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>72.2</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>71.8</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>72.8</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
         <is>
           <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>10/10</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2240,17 +2240,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,22 +2592,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,22 +3544,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,22 +3663,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5682,22 +5682,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6396,22 +6396,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,17 +6750,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6983,22 +6983,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -7498,32 +7498,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7531,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7555,17 +7559,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7575,17 +7579,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -7613,32 +7617,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7646,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7670,17 +7678,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7690,12 +7698,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7728,32 +7736,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7761,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7785,37 +7797,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -7843,32 +7855,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7876,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7900,37 +7916,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -7958,32 +7974,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7991,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8015,17 +8035,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8035,12 +8055,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8106,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8145,7 +8165,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8160,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8275,7 +8295,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8451,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8495,17 +8515,362 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
           <t>10/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>73.1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>8/10</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,17 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4025,17 +4025,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,22 +4139,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4739,17 +4739,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,22 +4972,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5449,17 +5449,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6044,17 +6044,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,17 +6163,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6515,22 +6515,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6869,17 +6869,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7340,22 +7340,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7460,17 +7460,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -7865,24 +7865,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7984,24 +7984,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -8093,32 +8093,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8126,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8150,17 +8154,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8170,17 +8174,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -8208,32 +8212,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8241,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8265,17 +8273,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8285,17 +8293,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -8323,32 +8331,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -8356,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8380,37 +8392,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -8438,32 +8450,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8471,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8495,17 +8511,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8515,12 +8531,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8586,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8625,7 +8641,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8640,7 +8656,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -8668,32 +8684,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8701,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8725,17 +8745,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8745,12 +8765,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8816,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8860,15 +8880,245 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>72.1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
         <is>
           <t>8/10</t>
         </is>

--- a/data/export/2026-10-01-182路.xlsx
+++ b/data/export/2026-10-01-182路.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6520,12 +6520,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6988,12 +6988,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7817,12 +7817,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7941,12 +7941,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8472,12 +8472,12 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8569,32 +8569,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8602,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8626,17 +8630,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8646,12 +8650,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8694,24 +8698,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8721,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8770,12 +8774,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -8803,32 +8807,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8836,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8860,17 +8868,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8880,12 +8888,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8918,32 +8926,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -8951,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8975,17 +8987,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -8995,12 +9007,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9066,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9110,12 +9122,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
